--- a/reference-smoke.xlsx
+++ b/reference-smoke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\excel-ai-addin-rc6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD96036C-E26D-4B6C-BA48-1B43E24723BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50ED0681-8914-4646-B678-EB4D3B24D769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -65,16 +65,10 @@
     <t>Ошибка</t>
   </si>
   <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
     <t>Москва</t>
   </si>
   <si>
     <t>Кофе</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
   </si>
   <si>
     <t>Казань</t>
@@ -83,19 +77,10 @@
     <t>Чай</t>
   </si>
   <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
     <t>Какао</t>
   </si>
   <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
     <t>Омск</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
   </si>
   <si>
     <t>Объединено A9:C9</t>
@@ -188,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -198,6 +183,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -289,19 +275,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Кофе</c:v>
+                  <c:v>Чай</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Чай</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Кофе</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Какао</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Кофе</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Чай</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -313,19 +299,19 @@
                 <c:formatCode>0.00\ \₽</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>840</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>520</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>1800</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>560</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -444,7 +430,9 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Товар"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Количество" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Цена"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Сумма"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Сумма">
+      <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ошибка"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -736,8 +724,11 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="526" row="8">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
 </wetp:taskpanes>
 </file>
@@ -752,12 +743,29 @@
 </we:webextension>
 </file>
 
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{BD76D9A1-5CE0-4EE7-8EA1-5F224C7E9A99}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;58f547de-b493-400c-b14d-bb98da680d7d&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H600"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,122 +787,1908 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>46267</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="F2" s="4">
         <f>D2*E2</f>
+        <v>840</v>
+      </c>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
+        <v>46270</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>280</v>
+      </c>
+      <c r="F3" s="4">
+        <f>D3*E3</f>
+        <v>1400</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>46266</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>450</v>
+      </c>
+      <c r="F4" s="4">
+        <f>D4*E4</f>
         <v>900</v>
       </c>
-      <c r="G2" t="e">
+      <c r="G4" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>46268</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>280</v>
-      </c>
-      <c r="F3" s="4">
-        <f>D3*E3</f>
-        <v>840</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>520</v>
-      </c>
-      <c r="F4" s="4">
-        <f>D4*E4</f>
-        <v>520</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>450</v>
       </c>
       <c r="F5" s="4">
         <f>D5*E5</f>
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>520</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>46269</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="F6" s="4">
         <f>D6*E6</f>
-        <v>560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1800</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H116" s="3"/>
+    </row>
+    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H122" s="3"/>
+    </row>
+    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H126" s="3"/>
+    </row>
+    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H134" s="3"/>
+    </row>
+    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H136" s="3"/>
+    </row>
+    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H137" s="3"/>
+    </row>
+    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H140" s="3"/>
+    </row>
+    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H141" s="3"/>
+    </row>
+    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H142" s="3"/>
+    </row>
+    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H146" s="3"/>
+    </row>
+    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H149" s="3"/>
+    </row>
+    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H154" s="3"/>
+    </row>
+    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H157" s="3"/>
+    </row>
+    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H158" s="3"/>
+    </row>
+    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H161" s="3"/>
+    </row>
+    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H162" s="3"/>
+    </row>
+    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H165" s="3"/>
+    </row>
+    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H166" s="3"/>
+    </row>
+    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H167" s="3"/>
+    </row>
+    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H168" s="3"/>
+    </row>
+    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H169" s="3"/>
+    </row>
+    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H171" s="3"/>
+    </row>
+    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H172" s="3"/>
+    </row>
+    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H173" s="3"/>
+    </row>
+    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H174" s="3"/>
+    </row>
+    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H175" s="3"/>
+    </row>
+    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H177" s="3"/>
+    </row>
+    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H178" s="3"/>
+    </row>
+    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H179" s="3"/>
+    </row>
+    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H180" s="3"/>
+    </row>
+    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H181" s="3"/>
+    </row>
+    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H182" s="3"/>
+    </row>
+    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H183" s="3"/>
+    </row>
+    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H185" s="3"/>
+    </row>
+    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H186" s="3"/>
+    </row>
+    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H187" s="3"/>
+    </row>
+    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H188" s="3"/>
+    </row>
+    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H189" s="3"/>
+    </row>
+    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H190" s="3"/>
+    </row>
+    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H191" s="3"/>
+    </row>
+    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H192" s="3"/>
+    </row>
+    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H193" s="3"/>
+    </row>
+    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H194" s="3"/>
+    </row>
+    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H195" s="3"/>
+    </row>
+    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H196" s="3"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H197" s="3"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H198" s="3"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H199" s="3"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H200" s="3"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H201" s="3"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H202" s="3"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H203" s="3"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H204" s="3"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H205" s="3"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H206" s="3"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H207" s="3"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H208" s="3"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H209" s="3"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H210" s="3"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H211" s="3"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H212" s="3"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H213" s="3"/>
+    </row>
+    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H214" s="3"/>
+    </row>
+    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H215" s="3"/>
+    </row>
+    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H216" s="3"/>
+    </row>
+    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H217" s="3"/>
+    </row>
+    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H218" s="3"/>
+    </row>
+    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H219" s="3"/>
+    </row>
+    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H220" s="3"/>
+    </row>
+    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H221" s="3"/>
+    </row>
+    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H222" s="3"/>
+    </row>
+    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H223" s="3"/>
+    </row>
+    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H224" s="3"/>
+    </row>
+    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H225" s="3"/>
+    </row>
+    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H226" s="3"/>
+    </row>
+    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H227" s="3"/>
+    </row>
+    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H228" s="3"/>
+    </row>
+    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H229" s="3"/>
+    </row>
+    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H230" s="3"/>
+    </row>
+    <row r="231" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H231" s="3"/>
+    </row>
+    <row r="232" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H232" s="3"/>
+    </row>
+    <row r="233" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H233" s="3"/>
+    </row>
+    <row r="234" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H234" s="3"/>
+    </row>
+    <row r="235" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H235" s="3"/>
+    </row>
+    <row r="236" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H236" s="3"/>
+    </row>
+    <row r="237" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H237" s="3"/>
+    </row>
+    <row r="238" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H238" s="3"/>
+    </row>
+    <row r="239" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H239" s="3"/>
+    </row>
+    <row r="240" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H240" s="3"/>
+    </row>
+    <row r="241" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H241" s="3"/>
+    </row>
+    <row r="242" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H242" s="3"/>
+    </row>
+    <row r="243" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H243" s="3"/>
+    </row>
+    <row r="244" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H244" s="3"/>
+    </row>
+    <row r="245" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H245" s="3"/>
+    </row>
+    <row r="246" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H246" s="3"/>
+    </row>
+    <row r="247" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H247" s="3"/>
+    </row>
+    <row r="248" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H248" s="3"/>
+    </row>
+    <row r="249" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H249" s="3"/>
+    </row>
+    <row r="250" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H250" s="3"/>
+    </row>
+    <row r="251" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H251" s="3"/>
+    </row>
+    <row r="252" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H252" s="3"/>
+    </row>
+    <row r="253" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H253" s="3"/>
+    </row>
+    <row r="254" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H254" s="3"/>
+    </row>
+    <row r="255" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H255" s="3"/>
+    </row>
+    <row r="256" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H256" s="3"/>
+    </row>
+    <row r="257" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H257" s="3"/>
+    </row>
+    <row r="258" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H258" s="3"/>
+    </row>
+    <row r="259" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H259" s="3"/>
+    </row>
+    <row r="260" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H260" s="3"/>
+    </row>
+    <row r="261" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H261" s="3"/>
+    </row>
+    <row r="262" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H262" s="3"/>
+    </row>
+    <row r="263" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H263" s="3"/>
+    </row>
+    <row r="264" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H264" s="3"/>
+    </row>
+    <row r="265" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H265" s="3"/>
+    </row>
+    <row r="266" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H266" s="3"/>
+    </row>
+    <row r="267" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H267" s="3"/>
+    </row>
+    <row r="268" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H268" s="3"/>
+    </row>
+    <row r="269" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H269" s="3"/>
+    </row>
+    <row r="270" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H270" s="3"/>
+    </row>
+    <row r="271" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H271" s="3"/>
+    </row>
+    <row r="272" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H272" s="3"/>
+    </row>
+    <row r="273" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H273" s="3"/>
+    </row>
+    <row r="274" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H274" s="3"/>
+    </row>
+    <row r="275" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H275" s="3"/>
+    </row>
+    <row r="276" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H276" s="3"/>
+    </row>
+    <row r="277" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H277" s="3"/>
+    </row>
+    <row r="278" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H278" s="3"/>
+    </row>
+    <row r="279" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H279" s="3"/>
+    </row>
+    <row r="280" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H280" s="3"/>
+    </row>
+    <row r="281" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H281" s="3"/>
+    </row>
+    <row r="282" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H282" s="3"/>
+    </row>
+    <row r="283" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H283" s="3"/>
+    </row>
+    <row r="284" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H284" s="3"/>
+    </row>
+    <row r="285" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H285" s="3"/>
+    </row>
+    <row r="286" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H286" s="3"/>
+    </row>
+    <row r="287" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H287" s="3"/>
+    </row>
+    <row r="288" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H288" s="3"/>
+    </row>
+    <row r="289" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H289" s="3"/>
+    </row>
+    <row r="290" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H290" s="3"/>
+    </row>
+    <row r="291" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H291" s="3"/>
+    </row>
+    <row r="292" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H292" s="3"/>
+    </row>
+    <row r="293" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H293" s="3"/>
+    </row>
+    <row r="294" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H294" s="3"/>
+    </row>
+    <row r="295" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H295" s="3"/>
+    </row>
+    <row r="296" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H296" s="3"/>
+    </row>
+    <row r="297" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H297" s="3"/>
+    </row>
+    <row r="298" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H298" s="3"/>
+    </row>
+    <row r="299" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H299" s="3"/>
+    </row>
+    <row r="300" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H300" s="3"/>
+    </row>
+    <row r="301" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H301" s="3"/>
+    </row>
+    <row r="302" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H302" s="3"/>
+    </row>
+    <row r="303" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H303" s="3"/>
+    </row>
+    <row r="304" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H304" s="3"/>
+    </row>
+    <row r="305" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H305" s="3"/>
+    </row>
+    <row r="306" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H306" s="3"/>
+    </row>
+    <row r="307" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H307" s="3"/>
+    </row>
+    <row r="308" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H308" s="3"/>
+    </row>
+    <row r="309" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H309" s="3"/>
+    </row>
+    <row r="310" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H310" s="3"/>
+    </row>
+    <row r="311" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H311" s="3"/>
+    </row>
+    <row r="312" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H312" s="3"/>
+    </row>
+    <row r="313" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H313" s="3"/>
+    </row>
+    <row r="314" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H314" s="3"/>
+    </row>
+    <row r="315" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H315" s="3"/>
+    </row>
+    <row r="316" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H316" s="3"/>
+    </row>
+    <row r="317" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H317" s="3"/>
+    </row>
+    <row r="318" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H318" s="3"/>
+    </row>
+    <row r="319" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H319" s="3"/>
+    </row>
+    <row r="320" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H320" s="3"/>
+    </row>
+    <row r="321" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H321" s="3"/>
+    </row>
+    <row r="322" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H322" s="3"/>
+    </row>
+    <row r="323" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H323" s="3"/>
+    </row>
+    <row r="324" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H324" s="3"/>
+    </row>
+    <row r="325" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H325" s="3"/>
+    </row>
+    <row r="326" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H326" s="3"/>
+    </row>
+    <row r="327" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H327" s="3"/>
+    </row>
+    <row r="328" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H328" s="3"/>
+    </row>
+    <row r="329" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H329" s="3"/>
+    </row>
+    <row r="330" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H330" s="3"/>
+    </row>
+    <row r="331" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H331" s="3"/>
+    </row>
+    <row r="332" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H332" s="3"/>
+    </row>
+    <row r="333" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H333" s="3"/>
+    </row>
+    <row r="334" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H334" s="3"/>
+    </row>
+    <row r="335" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H335" s="3"/>
+    </row>
+    <row r="336" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H336" s="3"/>
+    </row>
+    <row r="337" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H337" s="3"/>
+    </row>
+    <row r="338" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H338" s="3"/>
+    </row>
+    <row r="339" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H339" s="3"/>
+    </row>
+    <row r="340" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H340" s="3"/>
+    </row>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H341" s="3"/>
+    </row>
+    <row r="342" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H342" s="3"/>
+    </row>
+    <row r="343" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H343" s="3"/>
+    </row>
+    <row r="344" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H344" s="3"/>
+    </row>
+    <row r="345" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H345" s="3"/>
+    </row>
+    <row r="346" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H346" s="3"/>
+    </row>
+    <row r="347" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H347" s="3"/>
+    </row>
+    <row r="348" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H348" s="3"/>
+    </row>
+    <row r="349" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H349" s="3"/>
+    </row>
+    <row r="350" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H350" s="3"/>
+    </row>
+    <row r="351" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H351" s="3"/>
+    </row>
+    <row r="352" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H352" s="3"/>
+    </row>
+    <row r="353" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H353" s="3"/>
+    </row>
+    <row r="354" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H354" s="3"/>
+    </row>
+    <row r="355" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H355" s="3"/>
+    </row>
+    <row r="356" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H356" s="3"/>
+    </row>
+    <row r="357" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H357" s="3"/>
+    </row>
+    <row r="358" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H358" s="3"/>
+    </row>
+    <row r="359" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H359" s="3"/>
+    </row>
+    <row r="360" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H360" s="3"/>
+    </row>
+    <row r="361" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H361" s="3"/>
+    </row>
+    <row r="362" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H362" s="3"/>
+    </row>
+    <row r="363" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H363" s="3"/>
+    </row>
+    <row r="364" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H364" s="3"/>
+    </row>
+    <row r="365" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H365" s="3"/>
+    </row>
+    <row r="366" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H366" s="3"/>
+    </row>
+    <row r="367" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H367" s="3"/>
+    </row>
+    <row r="368" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H368" s="3"/>
+    </row>
+    <row r="369" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H369" s="3"/>
+    </row>
+    <row r="370" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H370" s="3"/>
+    </row>
+    <row r="371" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H371" s="3"/>
+    </row>
+    <row r="372" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H372" s="3"/>
+    </row>
+    <row r="373" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H373" s="3"/>
+    </row>
+    <row r="374" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H374" s="3"/>
+    </row>
+    <row r="375" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H375" s="3"/>
+    </row>
+    <row r="376" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H376" s="3"/>
+    </row>
+    <row r="377" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H377" s="3"/>
+    </row>
+    <row r="378" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H378" s="3"/>
+    </row>
+    <row r="379" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H379" s="3"/>
+    </row>
+    <row r="380" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H380" s="3"/>
+    </row>
+    <row r="381" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H381" s="3"/>
+    </row>
+    <row r="382" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H382" s="3"/>
+    </row>
+    <row r="383" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H383" s="3"/>
+    </row>
+    <row r="384" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H384" s="3"/>
+    </row>
+    <row r="385" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H385" s="3"/>
+    </row>
+    <row r="386" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H386" s="3"/>
+    </row>
+    <row r="387" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H387" s="3"/>
+    </row>
+    <row r="388" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H388" s="3"/>
+    </row>
+    <row r="389" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H389" s="3"/>
+    </row>
+    <row r="390" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H390" s="3"/>
+    </row>
+    <row r="391" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H391" s="3"/>
+    </row>
+    <row r="392" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H392" s="3"/>
+    </row>
+    <row r="393" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H393" s="3"/>
+    </row>
+    <row r="394" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H394" s="3"/>
+    </row>
+    <row r="395" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H395" s="3"/>
+    </row>
+    <row r="396" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H396" s="3"/>
+    </row>
+    <row r="397" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H397" s="3"/>
+    </row>
+    <row r="398" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H398" s="3"/>
+    </row>
+    <row r="399" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H399" s="3"/>
+    </row>
+    <row r="400" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H400" s="3"/>
+    </row>
+    <row r="401" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H401" s="3"/>
+    </row>
+    <row r="402" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H402" s="3"/>
+    </row>
+    <row r="403" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H403" s="3"/>
+    </row>
+    <row r="404" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H404" s="3"/>
+    </row>
+    <row r="405" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H405" s="3"/>
+    </row>
+    <row r="406" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H406" s="3"/>
+    </row>
+    <row r="407" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H407" s="3"/>
+    </row>
+    <row r="408" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H408" s="3"/>
+    </row>
+    <row r="409" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H409" s="3"/>
+    </row>
+    <row r="410" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H410" s="3"/>
+    </row>
+    <row r="411" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H411" s="3"/>
+    </row>
+    <row r="412" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H412" s="3"/>
+    </row>
+    <row r="413" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H413" s="3"/>
+    </row>
+    <row r="414" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H414" s="3"/>
+    </row>
+    <row r="415" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H415" s="3"/>
+    </row>
+    <row r="416" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H416" s="3"/>
+    </row>
+    <row r="417" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H417" s="3"/>
+    </row>
+    <row r="418" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H418" s="3"/>
+    </row>
+    <row r="419" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H419" s="3"/>
+    </row>
+    <row r="420" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H420" s="3"/>
+    </row>
+    <row r="421" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H421" s="3"/>
+    </row>
+    <row r="422" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H422" s="3"/>
+    </row>
+    <row r="423" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H423" s="3"/>
+    </row>
+    <row r="424" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H424" s="3"/>
+    </row>
+    <row r="425" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H425" s="3"/>
+    </row>
+    <row r="426" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H426" s="3"/>
+    </row>
+    <row r="427" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H427" s="3"/>
+    </row>
+    <row r="428" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H428" s="3"/>
+    </row>
+    <row r="429" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H429" s="3"/>
+    </row>
+    <row r="430" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H430" s="3"/>
+    </row>
+    <row r="431" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H431" s="3"/>
+    </row>
+    <row r="432" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H432" s="3"/>
+    </row>
+    <row r="433" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H433" s="3"/>
+    </row>
+    <row r="434" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H434" s="3"/>
+    </row>
+    <row r="435" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H435" s="3"/>
+    </row>
+    <row r="436" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H436" s="3"/>
+    </row>
+    <row r="437" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H437" s="3"/>
+    </row>
+    <row r="438" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H438" s="3"/>
+    </row>
+    <row r="439" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H439" s="3"/>
+    </row>
+    <row r="440" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H440" s="3"/>
+    </row>
+    <row r="441" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H441" s="3"/>
+    </row>
+    <row r="442" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H442" s="3"/>
+    </row>
+    <row r="443" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H443" s="3"/>
+    </row>
+    <row r="444" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H444" s="3"/>
+    </row>
+    <row r="445" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H445" s="3"/>
+    </row>
+    <row r="446" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H446" s="3"/>
+    </row>
+    <row r="447" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H447" s="3"/>
+    </row>
+    <row r="448" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H448" s="3"/>
+    </row>
+    <row r="449" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H449" s="3"/>
+    </row>
+    <row r="450" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H450" s="3"/>
+    </row>
+    <row r="451" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H451" s="3"/>
+    </row>
+    <row r="452" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H452" s="3"/>
+    </row>
+    <row r="453" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H453" s="3"/>
+    </row>
+    <row r="454" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H454" s="3"/>
+    </row>
+    <row r="455" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H455" s="3"/>
+    </row>
+    <row r="456" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H456" s="3"/>
+    </row>
+    <row r="457" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H457" s="3"/>
+    </row>
+    <row r="458" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H458" s="3"/>
+    </row>
+    <row r="459" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H459" s="3"/>
+    </row>
+    <row r="460" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H460" s="3"/>
+    </row>
+    <row r="461" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H461" s="3"/>
+    </row>
+    <row r="462" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H462" s="3"/>
+    </row>
+    <row r="463" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H463" s="3"/>
+    </row>
+    <row r="464" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H464" s="3"/>
+    </row>
+    <row r="465" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H465" s="3"/>
+    </row>
+    <row r="466" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H466" s="3"/>
+    </row>
+    <row r="467" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H467" s="3"/>
+    </row>
+    <row r="468" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H468" s="3"/>
+    </row>
+    <row r="469" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H469" s="3"/>
+    </row>
+    <row r="470" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H470" s="3"/>
+    </row>
+    <row r="471" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H471" s="3"/>
+    </row>
+    <row r="472" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H472" s="3"/>
+    </row>
+    <row r="473" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H473" s="3"/>
+    </row>
+    <row r="474" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H474" s="3"/>
+    </row>
+    <row r="475" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H475" s="3"/>
+    </row>
+    <row r="476" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H476" s="3"/>
+    </row>
+    <row r="477" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H477" s="3"/>
+    </row>
+    <row r="478" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H478" s="3"/>
+    </row>
+    <row r="479" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H479" s="3"/>
+    </row>
+    <row r="480" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H480" s="3"/>
+    </row>
+    <row r="481" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H481" s="3"/>
+    </row>
+    <row r="482" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H482" s="3"/>
+    </row>
+    <row r="483" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H483" s="3"/>
+    </row>
+    <row r="484" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H484" s="3"/>
+    </row>
+    <row r="485" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H485" s="3"/>
+    </row>
+    <row r="486" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H486" s="3"/>
+    </row>
+    <row r="487" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H487" s="3"/>
+    </row>
+    <row r="488" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H488" s="3"/>
+    </row>
+    <row r="489" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H489" s="3"/>
+    </row>
+    <row r="490" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H490" s="3"/>
+    </row>
+    <row r="491" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H491" s="3"/>
+    </row>
+    <row r="492" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H492" s="3"/>
+    </row>
+    <row r="493" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H493" s="3"/>
+    </row>
+    <row r="494" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H494" s="3"/>
+    </row>
+    <row r="495" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H495" s="3"/>
+    </row>
+    <row r="496" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H496" s="3"/>
+    </row>
+    <row r="497" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H497" s="3"/>
+    </row>
+    <row r="498" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H498" s="3"/>
+    </row>
+    <row r="499" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H499" s="3"/>
+    </row>
+    <row r="500" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H500" s="3"/>
+    </row>
+    <row r="501" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H501" s="3"/>
+    </row>
+    <row r="502" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H502" s="3"/>
+    </row>
+    <row r="503" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H503" s="3"/>
+    </row>
+    <row r="504" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H504" s="3"/>
+    </row>
+    <row r="505" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H505" s="3"/>
+    </row>
+    <row r="506" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H506" s="3"/>
+    </row>
+    <row r="507" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H507" s="3"/>
+    </row>
+    <row r="508" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H508" s="3"/>
+    </row>
+    <row r="509" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H509" s="3"/>
+    </row>
+    <row r="510" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H510" s="3"/>
+    </row>
+    <row r="511" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H511" s="3"/>
+    </row>
+    <row r="512" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H512" s="3"/>
+    </row>
+    <row r="513" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H513" s="3"/>
+    </row>
+    <row r="514" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H514" s="3"/>
+    </row>
+    <row r="515" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H515" s="3"/>
+    </row>
+    <row r="516" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H516" s="3"/>
+    </row>
+    <row r="517" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H517" s="3"/>
+    </row>
+    <row r="518" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H518" s="3"/>
+    </row>
+    <row r="519" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H519" s="3"/>
+    </row>
+    <row r="520" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H520" s="3"/>
+    </row>
+    <row r="521" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H521" s="3"/>
+    </row>
+    <row r="522" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H522" s="3"/>
+    </row>
+    <row r="523" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H523" s="3"/>
+    </row>
+    <row r="524" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H524" s="3"/>
+    </row>
+    <row r="525" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H525" s="3"/>
+    </row>
+    <row r="526" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H526" s="3"/>
+    </row>
+    <row r="527" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H527" s="3"/>
+    </row>
+    <row r="528" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H528" s="3"/>
+    </row>
+    <row r="529" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H529" s="3"/>
+    </row>
+    <row r="530" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H530" s="3"/>
+    </row>
+    <row r="531" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H531" s="3"/>
+    </row>
+    <row r="532" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H532" s="3"/>
+    </row>
+    <row r="533" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H533" s="3"/>
+    </row>
+    <row r="534" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H534" s="3"/>
+    </row>
+    <row r="535" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H535" s="3"/>
+    </row>
+    <row r="536" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H536" s="3"/>
+    </row>
+    <row r="537" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H537" s="3"/>
+    </row>
+    <row r="538" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H538" s="3"/>
+    </row>
+    <row r="539" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H539" s="3"/>
+    </row>
+    <row r="540" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H540" s="3"/>
+    </row>
+    <row r="541" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H541" s="3"/>
+    </row>
+    <row r="542" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H542" s="3"/>
+    </row>
+    <row r="543" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H543" s="3"/>
+    </row>
+    <row r="544" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H544" s="3"/>
+    </row>
+    <row r="545" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H545" s="3"/>
+    </row>
+    <row r="546" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H546" s="3"/>
+    </row>
+    <row r="547" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H547" s="3"/>
+    </row>
+    <row r="548" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H548" s="3"/>
+    </row>
+    <row r="549" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H549" s="3"/>
+    </row>
+    <row r="550" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H550" s="3"/>
+    </row>
+    <row r="551" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H551" s="3"/>
+    </row>
+    <row r="552" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H552" s="3"/>
+    </row>
+    <row r="553" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H553" s="3"/>
+    </row>
+    <row r="554" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H554" s="3"/>
+    </row>
+    <row r="555" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H555" s="3"/>
+    </row>
+    <row r="556" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H556" s="3"/>
+    </row>
+    <row r="557" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H557" s="3"/>
+    </row>
+    <row r="558" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H558" s="3"/>
+    </row>
+    <row r="559" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H559" s="3"/>
+    </row>
+    <row r="560" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H560" s="3"/>
+    </row>
+    <row r="561" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H561" s="3"/>
+    </row>
+    <row r="562" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H562" s="3"/>
+    </row>
+    <row r="563" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H563" s="3"/>
+    </row>
+    <row r="564" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H564" s="3"/>
+    </row>
+    <row r="565" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H565" s="3"/>
+    </row>
+    <row r="566" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H566" s="3"/>
+    </row>
+    <row r="567" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H567" s="3"/>
+    </row>
+    <row r="568" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H568" s="3"/>
+    </row>
+    <row r="569" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H569" s="3"/>
+    </row>
+    <row r="570" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H570" s="3"/>
+    </row>
+    <row r="571" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H571" s="3"/>
+    </row>
+    <row r="572" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H572" s="3"/>
+    </row>
+    <row r="573" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H573" s="3"/>
+    </row>
+    <row r="574" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H574" s="3"/>
+    </row>
+    <row r="575" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H575" s="3"/>
+    </row>
+    <row r="576" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H576" s="3"/>
+    </row>
+    <row r="577" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H577" s="3"/>
+    </row>
+    <row r="578" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H578" s="3"/>
+    </row>
+    <row r="579" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H579" s="3"/>
+    </row>
+    <row r="580" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H580" s="3"/>
+    </row>
+    <row r="581" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H581" s="3"/>
+    </row>
+    <row r="582" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H582" s="3"/>
+    </row>
+    <row r="583" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H583" s="3"/>
+    </row>
+    <row r="584" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H584" s="3"/>
+    </row>
+    <row r="585" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H585" s="3"/>
+    </row>
+    <row r="586" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H586" s="3"/>
+    </row>
+    <row r="587" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H587" s="3"/>
+    </row>
+    <row r="588" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H588" s="3"/>
+    </row>
+    <row r="589" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H589" s="3"/>
+    </row>
+    <row r="590" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H590" s="3"/>
+    </row>
+    <row r="591" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H591" s="3"/>
+    </row>
+    <row r="592" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H592" s="3"/>
+    </row>
+    <row r="593" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H593" s="3"/>
+    </row>
+    <row r="594" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H594" s="3"/>
+    </row>
+    <row r="595" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H595" s="3"/>
+    </row>
+    <row r="596" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H596" s="3"/>
+    </row>
+    <row r="597" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H597" s="3"/>
+    </row>
+    <row r="598" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H598" s="3"/>
+    </row>
+    <row r="599" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H599" s="3"/>
+    </row>
+    <row r="600" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H600" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -919,18 +2713,18 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0.15</v>
@@ -938,10 +2732,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0.1</v>
@@ -949,10 +2743,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>0.2</v>
@@ -973,18 +2767,18 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <f>SUMIF(Продажи!$B$2:$B$6,A2,Продажи!$F$2:$F$6)</f>
@@ -992,7 +2786,7 @@
       </c>
       <c r="C2">
         <f>B2/SUM($B$2:$B$4)</f>
-        <v>0.30735930735930733</v>
+        <v>0.26007326007326009</v>
       </c>
       <c r="E2">
         <f>COUNTA(Справочник!A2:A4)</f>
@@ -1001,20 +2795,20 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <f>SUMIF(Продажи!$B$2:$B$6,A3,Продажи!$F$2:$F$6)</f>
-        <v>1400</v>
+        <v>2240</v>
       </c>
       <c r="C3">
         <f>B3/SUM($B$2:$B$4)</f>
-        <v>0.30303030303030304</v>
+        <v>0.41025641025641024</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <f>SUMIF(Продажи!$B$2:$B$6,A4,Продажи!$F$2:$F$6)</f>
@@ -1022,7 +2816,7 @@
       </c>
       <c r="C4">
         <f>B4/SUM($B$2:$B$4)</f>
-        <v>0.38961038961038963</v>
+        <v>0.32967032967032966</v>
       </c>
     </row>
   </sheetData>
@@ -1037,13 +2831,13 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>Продажи!F2</f>
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +2862,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/reference-smoke.xlsx
+++ b/reference-smoke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\excel-ai-addin-rc6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FF9C2D-CA5C-490F-AF51-EDAF60ADF450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802338F8-C6C8-4B05-84D8-AB202B73286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0FB6-4409-9463-A3A011CF0EDE}"/>
+              <c16:uniqueId val="{00000000-A01A-497E-BDC6-043F61422756}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -705,14 +705,14 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="598" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="568" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
 <file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{79E56172-D7BD-4764-A962-86FD873178A2}">
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{4A988416-8916-45B0-B88A-55B52BA7E13D}">
   <we:reference id="5f2c9a41-1f7c-4f2b-9a0e-9c1f2d7b3e10" version="1.0.0.0" store="\\localhost\C$\Users\1\Desktop\excel-ai-addin-rc6\catalog" storeType="Filesystem"/>
   <we:alternateReferences/>
   <we:properties/>
@@ -794,10 +794,6 @@
         <f>D3*E3</f>
         <v>840</v>
       </c>
-      <c r="G3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -819,10 +815,6 @@
         <f>D4*E4</f>
         <v>520</v>
       </c>
-      <c r="G4" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -844,10 +836,6 @@
         <f>D5*E5</f>
         <v>1800</v>
       </c>
-      <c r="G5" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -868,10 +856,6 @@
       <c r="F6">
         <f>D6*E6</f>
         <v>560</v>
-      </c>
-      <c r="G6" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
